--- a/catalogs/MASTER_RESOURCE_CATALOG.xlsx
+++ b/catalogs/MASTER_RESOURCE_CATALOG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER_RESOURCE_CATALOG" sheetId="1" r:id="Rf40e4809951a44f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER_RESOURCE_CATALOG" sheetId="1" r:id="R06ed4058734a4e37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,7 +30,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -52,6 +52,11 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2436"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -60,7 +65,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -99,6 +104,10 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -336,94 +345,94 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="45" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="17" t="str">
         <x:v>resource_id</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="17" t="str">
         <x:v>title</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="17" t="str">
         <x:v>primary_chapter</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="17" t="str">
         <x:v>formats</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
+      <x:c r="E1" s="17" t="str">
         <x:v>purpose</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="F1" s="17" t="str">
         <x:v>version</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="str">
+      <x:c r="G1" s="17" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="H1" s="17" t="str">
         <x:v>aligned_chapters</x:v>
       </x:c>
-      <x:c r="I1" s="9" t="str">
+      <x:c r="I1" s="17" t="str">
         <x:v>folder</x:v>
       </x:c>
-      <x:c r="J1" s="9" t="str">
+      <x:c r="J1" s="17" t="str">
         <x:v>primary_chapter_title</x:v>
       </x:c>
-      <x:c r="K1" s="9" t="str">
+      <x:c r="K1" s="17" t="str">
         <x:v>related_resources</x:v>
       </x:c>
-      <x:c r="L1" s="9" t="str">
+      <x:c r="L1" s="17" t="str">
         <x:v>tier</x:v>
       </x:c>
-      <x:c r="M1" s="9" t="str">
+      <x:c r="M1" s="17" t="str">
         <x:v>legacy_aliases</x:v>
       </x:c>
-      <x:c r="N1" s="9" t="str">
+      <x:c r="N1" s="17" t="str">
         <x:v>has_browser_form</x:v>
       </x:c>
-      <x:c r="O1" s="9" t="str">
+      <x:c r="O1" s="17" t="str">
         <x:v>browser_form_path</x:v>
       </x:c>
-      <x:c r="P1" s="9" t="str">
+      <x:c r="P1" s="17" t="str">
         <x:v>has_process_flow</x:v>
       </x:c>
-      <x:c r="Q1" s="9" t="str">
+      <x:c r="Q1" s="17" t="str">
         <x:v>process_flow_path</x:v>
       </x:c>
-      <x:c r="R1" s="9" t="str">
+      <x:c r="R1" s="17" t="str">
         <x:v>reader_level</x:v>
       </x:c>
-      <x:c r="S1" s="9" t="str">
+      <x:c r="S1" s="17" t="str">
         <x:v>primary_audience</x:v>
       </x:c>
-      <x:c r="T1" s="9" t="str">
+      <x:c r="T1" s="17" t="str">
         <x:v>estimated_time</x:v>
       </x:c>
-      <x:c r="U1" s="9" t="str">
+      <x:c r="U1" s="17" t="str">
         <x:v>required_inputs</x:v>
       </x:c>
-      <x:c r="V1" s="9" t="str">
+      <x:c r="V1" s="17" t="str">
         <x:v>expected_output</x:v>
       </x:c>
-      <x:c r="W1" s="9" t="str">
+      <x:c r="W1" s="17" t="str">
         <x:v>prerequisites</x:v>
       </x:c>
-      <x:c r="X1" s="9" t="str">
+      <x:c r="X1" s="17" t="str">
         <x:v>use_frequency</x:v>
       </x:c>
-      <x:c r="Y1" s="9" t="str">
+      <x:c r="Y1" s="17" t="str">
         <x:v>essential_or_optional</x:v>
       </x:c>
-      <x:c r="Z1" s="9" t="str">
+      <x:c r="Z1" s="17" t="str">
         <x:v>recommended_format</x:v>
       </x:c>
-      <x:c r="AA1" s="9" t="str">
+      <x:c r="AA1" s="17" t="str">
         <x:v>technical_skill_required</x:v>
       </x:c>
-      <x:c r="AB1" s="9" t="str">
+      <x:c r="AB1" s="17" t="str">
         <x:v>reader_pathway</x:v>
       </x:c>
-      <x:c r="AC1" s="9" t="str">
+      <x:c r="AC1" s="17" t="str">
         <x:v>default_visibility</x:v>
       </x:c>
-      <x:c r="AD1" s="9" t="str">
+      <x:c r="AD1" s="17" t="str">
         <x:v>release_date</x:v>
       </x:c>
     </x:row>
@@ -438,7 +447,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E2" s="12" t="str">
         <x:v>Define the service problem, full intervention, realistic comparators, outcomes, value mechanism, decision rule, and review cycle.</x:v>
@@ -530,7 +539,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E3" s="14" t="str">
         <x:v>Identify affected parties, decision rights, participation duties, evidence contributions, and escalation authority.</x:v>
@@ -622,7 +631,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="12" t="str">
-        <x:v>md; docx; xlsx; csv; json</x:v>
+        <x:v>docx; xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str">
         <x:v>Provide a consistent problem-first, evidence, economic, governance, and lifecycle method for analysing worked and local cases.</x:v>
@@ -708,7 +717,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
         <x:v>Which intervention should the hospital test first when AI, staffing, and process redesign compete for the same limited resources?</x:v>
@@ -794,7 +803,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
         <x:v>Identify recurring technology-led, economic, workflow, evidence, governance, procurement, and lifecycle failures and record preventive controls.</x:v>
@@ -882,7 +891,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
         <x:v>Capture the initiating problem, project scope, accountable owners, affected groups, and decision rights.</x:v>
@@ -970,7 +979,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
         <x:v>Define the problem, population, intended users, intervention bundle, comparator, outcomes, and initial risks.</x:v>
@@ -1058,7 +1067,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
         <x:v>Specify population, intervention, comparator, outcomes, perspective, setting, time horizon, and decision rule.</x:v>
@@ -1146,7 +1155,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
         <x:v>Assess strategic, data, infrastructure, workflow, workforce, quality, economic, governance, procurement, and continuing support readiness.</x:v>
@@ -1238,7 +1247,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
         <x:v>Document source and derived data assets, authority, definitions, transformations, quality, lineage, monitoring, and remediation.</x:v>
@@ -1330,7 +1339,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
         <x:v>Is the organization ready to validate and pilot a readmission-risk model, and which capability gaps must be remediated first?</x:v>
@@ -1416,7 +1425,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
         <x:v>Assess strategic, data, infrastructure, workforce, governance, economic, ethical, security, and monitoring readiness at organizational and use-case levels.</x:v>
@@ -1504,7 +1513,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D14" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E14" s="12" t="str">
         <x:v>Document data sources, access authority, interoperability, quality, provenance, and reuse constraints.</x:v>
@@ -1592,7 +1601,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
         <x:v>Rate health-system maturity by domain and identify the weakest critical capability and prerequisites before pilot or scale.</x:v>
@@ -1680,7 +1689,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D16" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E16" s="12" t="str">
         <x:v>Authorize secondary data use through purpose, harmonization, access, risk, public value, and audit controls.</x:v>
@@ -1768,7 +1777,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
         <x:v>Assess completeness, plausibility, consistency, timeliness, representativeness, lineage, and actionability.</x:v>
@@ -1856,7 +1865,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D18" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E18" s="12" t="str">
         <x:v>Profiles missingness, duplicates, implausible values, subgroup coverage, and terminology-mapping completeness before AI validation or economic analysis.</x:v>
@@ -1942,7 +1951,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
         <x:v>Shows how complete-case analysis, simple imputation, and best/worst-case assumptions can change estimated outcomes and costs.</x:v>
@@ -2028,7 +2037,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D20" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E20" s="12" t="str">
         <x:v>Uses standardized features and k-means clustering to identify groups with different utilization, risk, cost, or workflow patterns.</x:v>
@@ -2114,7 +2123,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
         <x:v>Assign accountability, responsibility, consultation, information, escalation, pause, update, restart, and retirement authority.</x:v>
@@ -2206,7 +2215,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D22" s="12" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E22" s="12" t="str">
         <x:v>Which alert threshold produces an operationally safe balance between missed deterioration and review burden?</x:v>
@@ -2292,7 +2301,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
         <x:v>Evaluate whether and under what conditions a command dashboard should be scaled as a permanent patient-flow management intervention.</x:v>
@@ -2378,7 +2387,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D24" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E24" s="12" t="str">
         <x:v>Assign accountable and responsible owners, consultation, information, escalation, pause, update, restart, and retirement authority.</x:v>
@@ -2466,7 +2475,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
         <x:v>Compares prediction-model net benefit with treat-all and treat-none strategies across clinically relevant thresholds.</x:v>
@@ -2552,7 +2561,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D26" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E26" s="12" t="str">
         <x:v>Simulates arrivals, queues, service times, capacity, prioritization, and delays to assess how AI-enabled triage or scheduling affects operations.</x:v>
@@ -2638,7 +2647,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
         <x:v>Fits simple trend and exponential-smoothing forecasts to operational or financial time series and compares forecast accuracy.</x:v>
@@ -2724,7 +2733,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D28" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E28" s="12" t="str">
         <x:v>Selects an allocation across candidate AI or service options to maximize expected value subject to budget, workforce, capacity, and minimum-service constraints.</x:v>
@@ -2810,7 +2819,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
         <x:v>Translate claimed benefits into measurable mechanisms, owners, baselines, conversion conditions, and realized results.</x:v>
@@ -2902,7 +2911,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D30" s="12" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E30" s="12" t="str">
         <x:v>How much of the claimed notes time saving becomes usable capacity after review, correction, adoption, and implementation costs?</x:v>
@@ -2988,7 +2997,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
         <x:v>Select CFIR, NASSS-CAT, RE-AIM/PRISM, TAM/UTAUT, and mixed-method approaches according to the implementation question rather than name recognition.</x:v>
@@ -3076,7 +3085,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D32" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E32" s="12" t="str">
         <x:v>Assign each benefit to a mechanism, measure, owner, baseline, timing, accounting treatment, and verification source.</x:v>
@@ -3164,7 +3173,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E33" s="14" t="str">
         <x:v>Distinguish gross time saved, review burden, capacity released, capacity used, and realized value.</x:v>
@@ -3252,7 +3261,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D34" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E34" s="12" t="str">
         <x:v>Explores feedback among training, trust, adoption, workforce capacity, workload, benefit realization, and support burden over time.</x:v>
@@ -3338,7 +3347,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E35" s="14" t="str">
         <x:v>Models heterogeneous clinicians whose adoption changes through training, peer influence, perceived usefulness, workload, and adverse incidents.</x:v>
@@ -3424,7 +3433,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E36" s="12" t="str">
         <x:v>Translates gross task-time savings into net time, usable capacity, realized output, quality-adjusted productivity, and economic value.</x:v>
@@ -3510,7 +3519,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D37" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E37" s="14" t="str">
         <x:v>Integrate AI-enabled services into quality control, accreditation evidence, monitoring, thresholds, action, and closure.</x:v>
@@ -3602,7 +3611,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D38" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E38" s="12" t="str">
         <x:v>Document nonconformity, containment, causal analysis, corrective and preventive action, effectiveness, residual risk, and closure.</x:v>
@@ -3692,7 +3701,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D39" s="14" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E39" s="14" t="str">
         <x:v>When should a change in performance trigger investigation, restriction, and corrective action within the quality-management system?</x:v>
@@ -3778,7 +3787,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D40" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E40" s="12" t="str">
         <x:v>Select outcome, process, balancing, equity, workforce, economic, governance, and lifecycle indicators with definitions, owners, sources, thresholds, and actions.</x:v>
@@ -3866,7 +3875,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D41" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E41" s="14" t="str">
         <x:v>Summarizes numerical and categorical variables, compares groups, and creates baseline visual diagnostics before modeling.</x:v>
@@ -3952,7 +3961,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D42" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E42" s="12" t="str">
         <x:v>Define the economic decision, perspective, comparator, horizon, outcomes, costs, methods, uncertainty, safeguards, and validation.</x:v>
@@ -4044,7 +4053,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D43" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E43" s="14" t="str">
         <x:v>Record acquisition through exit costs, resource use, pricing exposure, opportunity cost, residual value, and evidence.</x:v>
@@ -4136,7 +4145,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D44" s="12" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E44" s="12" t="str">
         <x:v>Does the proposed AI service create value after all lifecycle costs, pricing exposure, and benefit-conversion conditions are included?</x:v>
@@ -4222,7 +4231,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D45" s="14" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E45" s="14" t="str">
         <x:v>How should released capacity, avoided resource use, cashable savings, revenue, accounting treatment, and budget incidence be distinguished?</x:v>
@@ -4308,7 +4317,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D46" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E46" s="12" t="str">
         <x:v>Specify the decision, perspective, comparator, costs, outcomes, horizon, uncertainty, distribution, and reporting plan.</x:v>
@@ -4396,7 +4405,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D47" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E47" s="14" t="str">
         <x:v>Model base and variable fees in clinically legible units, cap exposure, price support explicitly, and link renewal to realized value.</x:v>
@@ -4484,7 +4493,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D48" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E48" s="12" t="str">
         <x:v>Estimate incremental lifecycle costs from acquisition through operation, monitoring, material change, and exit.</x:v>
@@ -4572,7 +4581,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
         <x:v>Calculates one-time and recurring AI costs, discounted present value, cost per use, and optimistic/base/conservative scenarios across the full lifecycle.</x:v>
@@ -4658,7 +4667,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D50" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E50" s="12" t="str">
         <x:v>Calculates gross and risk-adjusted benefits, total cost, net benefit, ROI, payback period, and the effect of realization probability and attribution assumptions.</x:v>
@@ -4744,7 +4753,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
         <x:v>Summarize cost-effectiveness, affordability, distribution, HTA, reimbursement, adoption conditions, uncertainty, and recommendation.</x:v>
@@ -4836,7 +4845,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D52" s="12" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E52" s="12" t="str">
         <x:v>Can an intervention be cost-effective yet remain unaffordable or unsuitable for local adoption?</x:v>
@@ -4922,7 +4931,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
         <x:v>Compare incremental costs and outcomes, net benefit, affordability, uptake, cash flow, and sensitivity scenarios.</x:v>
@@ -5010,7 +5019,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D54" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E54" s="12" t="str">
         <x:v>Distinguish regulatory authorization, HTA, reimbursement or payment, procurement, and local adoption; record the authority, perspective, evidence, gaps, and continuing evidence conditions for each layer.</x:v>
@@ -5098,7 +5107,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
         <x:v>Compares an AI-enabled pathway with a comparator using incremental cost, incremental effect, ICER, net monetary benefit, and dominance rules.</x:v>
@@ -5184,7 +5193,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D56" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E56" s="12" t="str">
         <x:v>Estimates annual and cumulative financial consequences for a specific budget holder under low, base, and high adoption or effectiveness scenarios.</x:v>
@@ -5270,7 +5279,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D57" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
         <x:v>Compares costs, effects, net monetary benefit, access, and equity-weighted value across population groups.</x:v>
@@ -5356,7 +5365,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D58" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E58" s="12" t="str">
         <x:v>Select a decision model from the problem structure and document evidence, verification, uncertainty, and reproducibility.</x:v>
@@ -5448,7 +5457,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D59" s="14" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
         <x:v>Which uncertainty is most likely to change the adoption decision, and is further evidence worth its cost?</x:v>
@@ -5534,7 +5543,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D60" s="12" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E60" s="12" t="str">
         <x:v>Is an additional staged study worthwhile after accounting for expected information value, research cost, implementation delay, and sample size?</x:v>
@@ -5620,7 +5629,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
         <x:v>Examine uncertainty through alternative futures, thresholds, staged commitments, learning options, contract flexibility, and explicit exit criteria.</x:v>
@@ -5708,7 +5717,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D62" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E62" s="12" t="str">
         <x:v>Match evidence and assurance needs to reporting standards, appraisal tools, lifecycle guidance, and management systems.</x:v>
@@ -5796,7 +5805,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
         <x:v>Link each material claim and assumption to evidence, quality, applicability, uncertainty, owner, and action.</x:v>
@@ -5884,7 +5893,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D64" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E64" s="12" t="str">
         <x:v>Record the exact system, version, intended and prohibited uses, evidence, limitations, human oversight, and monitoring.</x:v>
@@ -5972,7 +5981,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
         <x:v>Select decision trees, Markov models, microsimulation, discrete-event simulation, system dynamics, or agent-based modeling by problem structure.</x:v>
@@ -6060,7 +6069,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D66" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E66" s="12" t="str">
         <x:v>Verify data provenance, environments, versioning, testing, validation, uncertainty, security, release, and archive controls.</x:v>
@@ -6148,7 +6157,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
         <x:v>Tests how one uncertain input at a time changes net monetary benefit or another linear decision outcome and ranks decision drivers.</x:v>
@@ -6234,7 +6243,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D68" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E68" s="12" t="str">
         <x:v>Propagates uncertainty in incremental costs and effects through Monte Carlo simulation, estimates cost-effectiveness probabilities across thresholds, and computes expected value of perfect information.</x:v>
@@ -6320,7 +6329,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
         <x:v>Calculates expected cost, effect, events, and net monetary benefit for short AI and comparator pathways with mutually exclusive outcome branches.</x:v>
@@ -6406,7 +6415,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D70" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E70" s="12" t="str">
         <x:v>Simulates repeated transitions among health states for AI and usual care, accumulating discounted costs and QALYs over time.</x:v>
@@ -6492,7 +6501,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
         <x:v>Simulates heterogeneous patients over repeated cycles so history, subgroup risk, adherence, and individual outcomes can affect AI value.</x:v>
@@ -6578,7 +6587,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D72" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E72" s="12" t="str">
         <x:v>Translate evidence, interoperability, data, security, monitoring, update, service, remedy, portability, and exit requirements into contract terms.</x:v>
@@ -6670,7 +6679,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
         <x:v>How should the hospital compare vendors when a lower price is accompanied by weak audit, security, update, and exit provisions?</x:v>
@@ -6756,7 +6765,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D74" s="12" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E74" s="12" t="str">
         <x:v>Does a change in the underlying model or hosting dependency require disclosure, revalidation, contractual action, and reauthorization?</x:v>
@@ -6842,7 +6851,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
         <x:v>Evaluate problem fit, evidence, integration, lifecycle cost, data rights, security, monitoring, updates, audit, and exit.</x:v>
@@ -6930,7 +6939,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D76" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E76" s="12" t="str">
         <x:v>Structure demonstrations around real workflows, evidence, limitations, usability, interoperability, monitoring, and unsupported claims.</x:v>
@@ -7018,7 +7027,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
         <x:v>Document intended use, evidence, audit, updates, data, security, service levels, pricing, termination, portability, and decommissioning clauses.</x:v>
@@ -7106,7 +7115,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D78" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E78" s="12" t="str">
         <x:v>Compares subscription, per-use, risk-sharing, and hybrid pricing arrangements under different volume, uptake, performance, and savings assumptions.</x:v>
@@ -7192,7 +7201,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
         <x:v>Ranks candidate AI products using weighted evidence domains while enforcing non-compensatory safety, privacy, equity, cybersecurity, audit, and exit safeguards.</x:v>
@@ -7278,7 +7287,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D80" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E80" s="12" t="str">
         <x:v>Review ethics, equity, privacy, cybersecurity, safety, continuity, trust, legal, and economic risks as one institutional system.</x:v>
@@ -7370,7 +7379,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
         <x:v>Define accurate, accessible communication about intended use, limitations, oversight, data, complaints, incidents, and alternatives.</x:v>
@@ -7462,7 +7471,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D82" s="12" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E82" s="12" t="str">
         <x:v>Which uses can be permitted when convenience and call reduction coexist with privacy, safety, equity, and communication risks?</x:v>
@@ -7548,7 +7557,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
         <x:v>Maintain date-stamped records for European, Romanian, and global legal, policy, standards, reimbursement, and guidance sources whose scope or implementation status may change.</x:v>
@@ -7636,7 +7645,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D84" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E84" s="12" t="str">
         <x:v>Record privacy, security, continuity, supplier, model, and incident risks with controls, owners, and review dates.</x:v>
@@ -7724,7 +7733,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
         <x:v>Identify affected groups, barriers, harms, mitigations, costs, residual concerns, and monitoring indicators.</x:v>
@@ -7812,7 +7821,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D86" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E86" s="12" t="str">
         <x:v>Translate autonomy, safety, transparency, fairness, oversight, accountability, and public value into evidence and action.</x:v>
@@ -7900,7 +7909,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
         <x:v>Explain AI use, limits, human oversight, data handling, accessibility, questions, complaints, incidents, and human alternatives.</x:v>
@@ -7988,7 +7997,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D88" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E88" s="12" t="str">
         <x:v>Establish a health-system governance charter covering purpose, scope, membership, evidence, decisions, monitoring, incidents, updates, and de-adoption.</x:v>
@@ -8076,7 +8085,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D89" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
         <x:v>Integrate trust-adjusted value, distributional effects, mitigation, public value, confidence, and mandatory safeguards.</x:v>
@@ -8164,7 +8173,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D90" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E90" s="12" t="str">
         <x:v>Fits a tree ensemble, calculates permutation importance, and visualizes the relationship between the top feature and predicted risk.</x:v>
@@ -8250,7 +8259,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
         <x:v>Compares AUC, calibration, sensitivity, specificity, predictive values, and selection rates across population groups.</x:v>
@@ -8336,7 +8345,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D92" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E92" s="12" t="str">
         <x:v>Scores inherent and residual risk, checks mitigation completeness, prioritizes overdue actions, and produces an accountable risk dashboard.</x:v>
@@ -8422,7 +8431,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D93" s="14" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E93" s="14" t="str">
         <x:v>Does local performance and observed service change support adoption, and what can reasonably be attributed to the AI-enabled pathway?</x:v>
@@ -8508,7 +8517,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D94" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E94" s="12" t="str">
         <x:v>Match evidence type and study stage to current reporting and appraisal instruments without treating checklist completion as proof of validity, effectiveness, or regulatory conformity.</x:v>
@@ -8596,7 +8605,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D95" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E95" s="14" t="str">
         <x:v>Appraise reference standards, index tests, data partitions, calibration, diagnostic accuracy, bias, subgroup performance, clinical utility, and downstream resource consequences.</x:v>
@@ -8684,7 +8693,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D96" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png; html</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E96" s="12" t="str">
         <x:v>Document intended use, local cohort, exact system version, discrimination, calibration, threshold-specific performance, subgroup findings, workflow, clinical utility, uncertainty, and the resulting local decision.</x:v>
@@ -8772,7 +8781,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D97" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E97" s="14" t="str">
         <x:v>Builds two baseline classifiers, compares test performance, and exports predictions for later validation modules.</x:v>
@@ -8858,7 +8867,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D98" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E98" s="12" t="str">
         <x:v>Calculates ROC AUC, Brier score, confusion-matrix measures across thresholds, calibration intercept and slope, and calibration bins.</x:v>
@@ -8944,7 +8953,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D99" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E99" s="14" t="str">
         <x:v>Evaluates change after an AI implementation using segmented regression, run charts, control limits, uptake, and balancing measures.</x:v>
@@ -9030,7 +9039,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D100" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E100" s="12" t="str">
         <x:v>Pools study-level effects using inverse-variance fixed and DerSimonian-Laird random-effects methods, quantifies heterogeneity, and creates forest and funnel plots.</x:v>
@@ -9116,7 +9125,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D101" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E101" s="14" t="str">
         <x:v>Estimates the effect of AI implementation by comparing change over time in an intervention group with change in a comparison group.</x:v>
@@ -9202,7 +9211,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D102" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E102" s="12" t="str">
         <x:v>Estimates Kaplan-Meier survival curves and compares event timing between AI and comparator groups using a log-rank test.</x:v>
@@ -9288,7 +9297,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D103" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E103" s="14" t="str">
         <x:v>Record the current institutional decision state, exact intervention identity, scope, evidence, conditions, safeguards, triggers, authority, history, and next review.</x:v>
@@ -9380,7 +9389,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D104" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E104" s="12" t="str">
         <x:v>Define recurring and event-triggered surveillance across technical, workflow, safety, equity, economic, and contractual domains.</x:v>
@@ -9472,7 +9481,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D105" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E105" s="14" t="str">
         <x:v>Reconstruct technical, clinical, workflow, privacy, cybersecurity, equity, communication, and economic incidents consistently.</x:v>
@@ -9564,7 +9573,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D106" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E106" s="12" t="str">
         <x:v>Assess material change, revalidation, current authorization, renewal, renegotiation, replacement, retirement, continuity, and the end of authorization.</x:v>
@@ -9656,7 +9665,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D107" s="14" t="str">
-        <x:v>md; csv; json; xlsx</x:v>
+        <x:v>xlsx; csv; json; md</x:v>
       </x:c>
       <x:c r="E107" s="14" t="str">
         <x:v>Should the organization continue, restrict, roll back, replace, or retire the system after a material update and operational incident?</x:v>
@@ -9742,7 +9751,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D108" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E108" s="12" t="str">
         <x:v>Distinguish legal instruments, standards, guidance, reporting guidelines, appraisal tools, implementation frameworks, and author-developed decision aids; select them according to function and authority.</x:v>
@@ -9830,7 +9839,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D109" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E109" s="14" t="str">
         <x:v>Review dossier completeness, confidence, inconsistencies, mandatory safeguards, decision readiness, and remediation.</x:v>
@@ -9918,7 +9927,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D110" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E110" s="12" t="str">
         <x:v>Apply the book architecture to an institutional case and produce a defendable decision with conditions and lifecycle controls.</x:v>
@@ -10006,7 +10015,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D111" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E111" s="14" t="str">
         <x:v>Maintain a controlled inventory of proposed and deployed AI systems, owners, versions, risk levels, and review dates.</x:v>
@@ -10094,7 +10103,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D112" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E112" s="12" t="str">
         <x:v>Document role, workflow, training, competency, downtime, escalation, refresh, and adoption requirements.</x:v>
@@ -10182,7 +10191,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D113" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E113" s="14" t="str">
         <x:v>Assess model, data, interface, workflow, vendor, contract, policy, performance, risk, and annual renewal changes.</x:v>
@@ -10270,7 +10279,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D114" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E114" s="12" t="str">
         <x:v>Classify and reconstruct technical, clinical, workflow, privacy, cybersecurity, equity, and communication incidents.</x:v>
@@ -10358,7 +10367,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D115" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E115" s="14" t="str">
         <x:v>Prepare a decision-ready executive recommendation, options, evidence, economics, residual risk, dissent, conditions, owners, and next review.</x:v>
@@ -10446,7 +10455,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D116" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E116" s="12" t="str">
         <x:v>Summarize the decision problem, comparator, evidence, economics, risks, implementation, conditions, and decision requested.</x:v>
@@ -10534,7 +10543,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D117" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E117" s="14" t="str">
         <x:v>Bundle lifecycle checklists for monitoring, version control, scn planning, policy updates, procurement, and decommissioning.</x:v>
@@ -10622,7 +10631,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D118" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E118" s="12" t="str">
         <x:v>Assess problem relevance, data, validity, economics, ethics, feasibility, lifecycle governance, safeguards, and final decision.</x:v>
@@ -10710,7 +10719,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D119" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E119" s="14" t="str">
         <x:v>Maintain a versioned evidence, economics, governance, implementation, monitoring, update, and decision record.</x:v>
@@ -10798,7 +10807,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D120" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E120" s="12" t="str">
         <x:v>Manage implementation as an evidence-producing sequence from problem verification through continuous evaluation.</x:v>
@@ -10886,7 +10895,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D121" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E121" s="14" t="str">
         <x:v>Operate daily technical checks, periodic service and economic review, incident classification, reconstruction, escalation, and annual renewal.</x:v>
@@ -10974,7 +10983,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D122" s="12" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E122" s="12" t="str">
         <x:v>Define stopping triggers, fallback, transition, data disposition, communication, contract exit, validation, and post-retirement review.</x:v>
@@ -11062,7 +11071,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D123" s="14" t="str">
-        <x:v>docx; xlsx; csv; json; md; mmd; svg; png</x:v>
+        <x:v>docx; xlsx; csv; json; md; mmd; svg</x:v>
       </x:c>
       <x:c r="E123" s="14" t="str">
         <x:v>Define construct, content, reliability, feasibility, decision, implementation, and prospective validation for proposed frameworks.</x:v>
@@ -11150,7 +11159,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D124" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E124" s="12" t="str">
         <x:v>Tracks discrimination, calibration error, score distribution, and feature drift across time periods.</x:v>
@@ -11236,7 +11245,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D125" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="E125" s="14" t="str">
         <x:v>Monitors technical, clinical, workflow, equity, economic, and trust indicators against warning and stop thresholds over time.</x:v>
